--- a/output/2026年5月/2026年5月党费汇总表.xlsx
+++ b/output/2026年5月/2026年5月党费汇总表.xlsx
@@ -523,7 +523,7 @@
         <v>37</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>174.5</v>
+        <v>169.7</v>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
     </row>
@@ -674,7 +674,7 @@
         <v>343</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>831.1999999999998</v>
+        <v>826.3999999999999</v>
       </c>
       <c r="E13" s="8" t="inlineStr"/>
     </row>
